--- a/songs/FridayImInLove_v1/quelle/struktur.xlsx
+++ b/songs/FridayImInLove_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>25</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>140</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>pause</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(4500, 5)   (Matrix: progScrollText("Friday im in Love by The Cure", 20500, 90, getRandomColor(), 10))</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4500, 5)   (Matrix: progScrollText("Friday im in Love by The Cure", 20500, 90, getRandomColor(), 10))</t>
         </is>
@@ -551,13 +566,19 @@
           <t>intro</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(13714, 6, 10)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13714, 6, 10)</t>
         </is>
@@ -572,13 +593,19 @@
           <t>intro 2</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13714, 1015, 15, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 1015, 15, 5, 26, 5, true, 3)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(13714, 3, 20)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 3, 20)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(13714, 6, 25)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 6, 25)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>Saturday went</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(10286, 30, 460, true)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(10286, 30, 460, true)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(13714, 7, 35)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 7, 35)</t>
         </is>
@@ -677,13 +728,19 @@
           <t>SOLO</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(13714, 2, 40, 1, 16, 2000)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13714, 2, 40, 1, 16, 2000)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>verse 3</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(13714, 2, 45)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 2, 45)</t>
         </is>
@@ -719,13 +782,19 @@
           <t>Saturday went</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progRandomLines(10286, 50, 460, true)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(10286, 50, 460, true)</t>
         </is>
@@ -740,13 +809,19 @@
           <t>dressed up</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13714, 430, 55, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 430, 55, 5, 26, 5, false, 4)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>dressed up 2</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(12000, 2, 57, 1, 16, 2000)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(12000, 2, 57, 1, 16, 2000)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>strobo</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1714, 60, 65, 255, 255, 255)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1714, 60, 65, 255, 255, 255)</t>
         </is>
@@ -803,13 +890,19 @@
           <t>verse 4a</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(13714, 2, 65)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 2, 65)</t>
         </is>
@@ -824,13 +917,19 @@
           <t>verse 4b</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(13714, 70, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(13714, 70, 50, true, false)</t>
         </is>
@@ -845,13 +944,19 @@
           <t>outro chorus 1</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(13714, 860, 75, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 860, 75, 5, 26, 5, true, 3)</t>
         </is>
@@ -866,13 +971,19 @@
           <t>outro chorus 2</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(12000, 2, 80, 1, 16, 2000)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(12000, 2, 80, 1, 16, 2000)</t>
         </is>
@@ -887,13 +998,19 @@
           <t>git fade out</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(5143, 85, 6000)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(5143, 85, 6000)</t>
         </is>
@@ -913,10 +1030,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/FridayImInLove_v1/quelle/struktur.xlsx
+++ b/songs/FridayImInLove_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>

--- a/songs/FridayImInLove_v1/quelle/struktur.xlsx
+++ b/songs/FridayImInLove_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>25</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>140</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4500, 5)   (Matrix: progScrollText("Friday im in Love by The Cure", 20500, 90, getRandomColor(), 10))</t>
         </is>
@@ -573,12 +583,17 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Einzelblitze bleiben, weich eingeblendet (fade_in 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13714, 6, 10)</t>
         </is>
@@ -601,12 +616,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, in SUNSET mit weichen Farbwechseln (soft 40); Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 1015, 15, 5, 26, 5, true, 3)</t>
         </is>
@@ -628,12 +648,17 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, SUNSET: warmes Farbband über die ganze Bühne, weich eingeblendet (fade, 2 Beats).</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 3, 20)</t>
         </is>
@@ -655,12 +680,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, SUNSET: dezenter Puls im Beat - kleine Steigerung.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 6, 25)</t>
         </is>
@@ -682,12 +712,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, NEON: Bühnenhälften blitzen abwechselnd im Beat. Fester Look für beide "Saturday went". Blinder auf die letzte Viertel (Takt 41,75).</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(10286, 30, 460, true)</t>
         </is>
@@ -709,12 +744,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, SUNSET, soft 100: die ganze Bühne fließt pro Beat in die nächste Farbe.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 7, 35)</t>
         </is>
@@ -736,12 +776,17 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Szene Solo Gitarre, NEON: zwei Kometen laufen um die Gitarre, alle anderen atmen dunkel. Übergang läuft über die Bühne zur Gitarre (stage_lr).</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13714, 2, 40, 1, 16, 2000)</t>
         </is>
@@ -763,12 +808,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene Rain, NEON, Farbwanderung (triad, 2 Takte).</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 2, 45)</t>
         </is>
@@ -790,12 +840,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal (Call Response, NEON); letzter Takt Szene Buildup (tail 4 Beats).</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(10286, 50, 460, true)</t>
         </is>
@@ -817,12 +872,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Stern, NEON, Blinder auf den Einsatz; Lampen blitzen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 430, 55, 5, 26, 5, false, 4)</t>
         </is>
@@ -844,12 +904,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Anwachsende Einzelblitze bleiben; drei kurze Blinder am Ende (Takt 86,5 / 86,75 und die 1 des Strobo-Takts 87).</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(12000, 2, 57, 1, 16, 2000)</t>
         </is>
@@ -871,12 +936,13 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1714, 60, 65, 255, 255, 255)</t>
         </is>
@@ -898,12 +964,17 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA, SUNSET: Helix dreht sich auf der Matrix, die Bühnenhälften pulsieren abwechselnd - Ruhe nach dem Strobo.</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 2, 65)</t>
         </is>
@@ -925,12 +996,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben; darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 8 Takte) - Anlauf zum Schluss.</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(13714, 70, 50, true, false)</t>
         </is>
@@ -952,12 +1028,17 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, FIRE, Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 860, 75, 5, 26, 5, true, 3)</t>
         </is>
@@ -979,12 +1060,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE; starker Blinder auf der letzten Viertel (Takt 118,75), klingt ins Fade-out aus (carry).</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(12000, 2, 80, 1, 16, 2000)</t>
         </is>
@@ -1006,12 +1092,17 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fadeout, SUNSET: blendet über die 3 Takte weich nach Schwarz.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(5143, 85, 6000)</t>
         </is>
@@ -1031,10 +1122,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>0</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/FridayImInLove_v1/quelle/struktur.xlsx
+++ b/songs/FridayImInLove_v1/quelle/struktur.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>progBlack(4500, 5)
+          <t>progBlack(4500, 3)
 Alles schwarz bis zum Intro (die Matrix zeigt den Titel-Lauftext).</t>
         </is>
       </c>
@@ -578,7 +578,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(13714, 6, 10)
+          <t>progFastBlingBling(13714, 6, 4)
 Alter Effekt: schnelle Einzelblitze.</t>
         </is>
       </c>
@@ -610,8 +610,8 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13715, 1015, 15, 5, 26, 5, true, 3)
-matrix: progSternNeu(13715, 1015, 15, 5, 26, 5, false, 4)
+          <t>progSternNeu(13715, 1015, 5, 5, 26, 5, true, 3)
+matrix: progSternNeu(13715, 1015, 5, 5, 26, 5, false, 4)
 Alter Effekt: drehender, wandernder Stern, Farbwechsel etwa alle 1 s (1015 ms, nicht im Beat-Raster). Auf der Matrix steht der Stern fest in der Mitte.</t>
         </is>
       </c>
@@ -643,7 +643,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>progPalette(13714, 3, 20)
+          <t>progPalette(13714, 3, 6)
 Alter Effekt: lila und grüne Balken mit dunklen Lücken laufen über die Geräte.</t>
         </is>
       </c>
@@ -675,7 +675,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>progPalette(13714, 6, 25)
+          <t>progPalette(13714, 6, 7)
 Alter Effekt: weiße Wellen, weich an- und abschwellend.</t>
         </is>
       </c>
@@ -707,7 +707,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(10286, 30, 460, true)
+          <t>progRandomLines(10286, 8, 460, true)
 Alter Effekt: alle 460 ms eine neue zufällige Linie in Zufallsfarbe (etwas langsamer als der Beat).</t>
         </is>
       </c>
@@ -739,7 +739,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>progPalette(13714, 7, 35)
+          <t>progPalette(13714, 7, 9)
 Alter Effekt: Wolken-Farben (blau, hellblau, weiß), ruhig.</t>
         </is>
       </c>
@@ -771,7 +771,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(13714, 2, 40, 1, 16, 2000)
+          <t>progFastBlingBling(13714, 2, 10, 1, 16, 2000)
 Alter Effekt: Einzelblitze, die über den Part dichter werden (alle 2 s eine LED mehr, bis 16).</t>
         </is>
       </c>
@@ -803,7 +803,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>progPalette(13715, 2, 45)
+          <t>progPalette(13715, 2, 11)
 Alter Effekt: Regenbogen-Streifen mit Lücken, weich überblendet.</t>
         </is>
       </c>
@@ -835,7 +835,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>progRandomLines(10285, 50, 460, true)
+          <t>progRandomLines(10285, 12, 460, true)
 Alter Effekt: alle 460 ms eine neue zufällige Linie in Zufallsfarbe (etwas langsamer als der Beat).</t>
         </is>
       </c>
@@ -867,7 +867,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13715, 429, 55, 5, 26, 5, false, 4)
+          <t>progSternNeu(13715, 429, 13, 5, 26, 5, false, 4)
 Alter Effekt: drehender Stern, fest in der Mitte, Farbwechsel pro Beat.</t>
         </is>
       </c>
@@ -899,7 +899,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(12000, 2, 60, 1, 16, 2000)
+          <t>progFastBlingBling(12000, 2, 14, 1, 16, 2000)
 Alter Effekt: Einzelblitze, die über den Part dichter werden (alle 2 s eine LED mehr, bis 16).</t>
         </is>
       </c>
@@ -931,7 +931,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>progStrobo(1714, 65, 65, 255, 255, 255)
+          <t>progStrobo(1714, 15, 65, 255, 255, 255)
 Alter Effekt: 1 Takt weißes Flimmern (65 ms).</t>
         </is>
       </c>
@@ -959,7 +959,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>progPalette(13714, 2, 70)
+          <t>progPalette(13714, 2, 16)
 Alter Effekt: Regenbogen-Streifen mit Lücken, weich überblendet (sehr farbig).</t>
         </is>
       </c>
@@ -991,7 +991,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>progWaterRipple(13715, 75, 50, true, false)
+          <t>progWaterRipple(13715, 17, 50, true, false)
 Alter Effekt: Wasserringe an zufälligen Stellen, mit Farbverlauf.</t>
         </is>
       </c>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>progSternNeu(13714, 857, 80, 5, 26, 5, true, 3)
+          <t>progSternNeu(13714, 857, 18, 5, 26, 5, true, 3)
 Alter Effekt: drehender, wandernder Stern, Farbwechsel alle 2 Beats.</t>
         </is>
       </c>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>progFastBlingBling(12000, 2, 85, 1, 16, 2000)
+          <t>progFastBlingBling(12000, 2, 19, 1, 16, 2000)
 Alter Effekt: Einzelblitze, die über den Part dichter werden (alle 2 s eine LED mehr, bis 16).</t>
         </is>
       </c>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>progBlingBlingColoring(5143, 90, 6000)
+          <t>progBlingBlingColoring(5143, 20, 6000)
 Alter Effekt: jedes Gerät füllt sich langsam LED für LED mit einer Farbe (ruhiger Ausklang).</t>
         </is>
       </c>

--- a/songs/FridayImInLove_v1/quelle/struktur.xlsx
+++ b/songs/FridayImInLove_v1/quelle/struktur.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,6 +39,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -54,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -71,6 +77,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,17 +445,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +482,7 @@
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -484,6 +495,7 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -496,6 +508,7 @@
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -515,25 +528,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Neuer Vorschlag (KI)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -556,12 +574,13 @@
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>progBlack(4500, 5)   (Matrix: progScrollText("Friday im in Love by The Cure", 20500, 90, getRandomColor(), 10))</t>
         </is>
@@ -583,17 +602,18 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Einzelblitze bleiben, weich eingeblendet (fade_in 4 Beats).</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13714, 6, 10)</t>
         </is>
@@ -616,17 +636,18 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Stern bleibt, in SUNSET mit weichen Farbwechseln (soft 40); Blinder auf den Einsatz (2 Beats).</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 1015, 15, 5, 26, 5, true, 3)</t>
         </is>
@@ -641,24 +662,30 @@
           <t>verse 1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_PLASMA, Farben SCHEME_SUNSET
+Strophe neu (18.10.2026, statt der alten Palette): warme Farbwolken auf der Matrix, der Verlauf dreht sich um Gitarre und Bass und steigt in den Lampen auf, alles schwillt im Beat leicht an</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 3, 6)
 Alter Effekt: lila und grüne Balken mit dunklen Lücken laufen über die Geräte.</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Szene Palette, SUNSET: warmes Farbband über die ganze Bühne, weich eingeblendet (fade, 2 Beats).</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 3, 20)</t>
         </is>
@@ -673,24 +700,30 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_PLASMA, Farben SCHEME_SUNSET
+wie verse 1: warme Farbwolken, die im Beat leicht anschwellen</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 6, 7)
 Alter Effekt: weiße Wellen, weich an- und abschwellend.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Szene Verse, SUNSET: dezenter Puls im Beat - kleine Steigerung.</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 6, 25)</t>
         </is>
@@ -712,17 +745,18 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Szene Call Response, NEON: Bühnenhälften blitzen abwechselnd im Beat. Fester Look für beide "Saturday went". Blinder auf die letzte Viertel (Takt 41,75).</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(10286, 30, 460, true)</t>
         </is>
@@ -737,24 +771,30 @@
           <t>verse 2</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_WAVES, Farben SCHEME_ICE
+Strophe neu (18.10.2026): Sinuswellen in Blau/Eisblau laufen im Takt über die Matrix ('Monday you can hold your head'), eine Lichtebene fährt je Takt über Gitarre und Bass, Lichtschuss in den Lampen</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 7, 9)
 Alter Effekt: Wolken-Farben (blau, hellblau, weiß), ruhig.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Szene Colors, SUNSET, soft 100: die ganze Bühne fließt pro Beat in die nächste Farbe.</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 7, 35)</t>
         </is>
@@ -776,17 +816,18 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Szene Solo Gitarre, NEON: zwei Kometen laufen um die Gitarre, alle anderen atmen dunkel. Übergang läuft über die Bühne zur Gitarre (stage_lr).</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(13714, 2, 40, 1, 16, 2000)</t>
         </is>
@@ -801,24 +842,30 @@
           <t>verse 3</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_WAVES, Farben SCHEME_ICE
+wie verse 2: Sinuswellen und Lichtebene im Takt in Blau/Eisblau</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>progPalette(13715, 2, 11)
 Alter Effekt: Regenbogen-Streifen mit Lücken, weich überblendet.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Szene Rain, NEON, Farbwanderung (triad, 2 Takte).</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 2, 45)</t>
         </is>
@@ -840,17 +887,18 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>wie beim ersten Mal (Call Response, NEON); letzter Takt Szene Buildup (tail 4 Beats).</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>progRandomLines(10286, 50, 460, true)</t>
         </is>
@@ -872,17 +920,18 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Stern, NEON, Blinder auf den Einsatz; Lampen blitzen weiß auf 2 und 4.</t>
         </is>
       </c>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 430, 55, 5, 26, 5, false, 4)</t>
         </is>
@@ -904,17 +953,18 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Anwachsende Einzelblitze bleiben; drei kurze Blinder am Ende (Takt 86,5 / 86,75 und die 1 des Strobo-Takts 87).</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(12000, 2, 57, 1, 16, 2000)</t>
         </is>
@@ -937,12 +987,13 @@
       </c>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1714, 60, 65, 255, 255, 255)</t>
         </is>
@@ -957,24 +1008,30 @@
           <t>verse 4a</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_HEART, Farben SCHEME_NEON
+Strophe neu (18.10.2026): 'Friday I'm in love' - alle Geräte schlagen auf jedem Beat wie ein Herz in Pink/Cyan/Violett, die Matrix zeigt eine Lissajous-Schleife</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 2, 16)
 Alter Effekt: Regenbogen-Streifen mit Lücken, weich überblendet (sehr farbig).</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Szene DNA, SUNSET: Helix dreht sich auf der Matrix, die Bühnenhälften pulsieren abwechselnd - Ruhe nach dem Strobo.</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>progPalette(13714, 2, 65)</t>
         </is>
@@ -996,17 +1053,18 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Wasserringe bleiben; darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 8 Takte) - Anlauf zum Schluss.</t>
         </is>
       </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(13714, 70, 50, true, false)</t>
         </is>
@@ -1028,17 +1086,18 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Szene Star, FIRE, Blinder auf den Einsatz (2 Beats).</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(13714, 860, 75, 5, 26, 5, true, 3)</t>
         </is>
@@ -1060,17 +1119,18 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>Szene Sparkle, FIRE; starker Blinder auf der letzten Viertel (Takt 118,75), klingt ins Fade-out aus (carry).</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(12000, 2, 80, 1, 16, 2000)</t>
         </is>
@@ -1092,17 +1152,18 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>Szene Fadeout, SUNSET: blendet über die 3 Takte weich nach Schwarz.</t>
         </is>
       </c>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(5143, 85, 6000)</t>
         </is>
@@ -1122,10 +1183,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <f>$C$3</f>
         <v/>
       </c>
